--- a/data/auxiliary/DIVIPOLA.xlsx
+++ b/data/auxiliary/DIVIPOLA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sofia\Desktop\Proyecto-Orquideas\data\auxiliary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CDB746F-5926-40BD-808D-E6E2DAB4B18C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B486C511-48F9-4AF5-951B-FE4F54315368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="ESRI_MAPINFO_SHEET" sheetId="5" state="veryHidden" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Municipios!$A$1:$D$1123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Municipios!$D$1:$D$1123</definedName>
     <definedName name="ODS_aglomeraciones_2003_2015" localSheetId="0">Municipios!#REF!</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -37013,7 +37013,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="D1:D1123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
@@ -37033,14 +37033,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="56e6d1e7-6899-430c-9877-67183cfe1730">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="12ae8c1a-628e-4358-b6c7-76504a3ed5f5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -37273,21 +37271,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="56e6d1e7-6899-430c-9877-67183cfe1730">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="12ae8c1a-628e-4358-b6c7-76504a3ed5f5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{447EAC8B-E01C-4BBA-8F26-CA458DD9CFEC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7556074-C591-45E1-B532-8E33AF3A1CB7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="56e6d1e7-6899-430c-9877-67183cfe1730"/>
-    <ds:schemaRef ds:uri="12ae8c1a-628e-4358-b6c7-76504a3ed5f5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -37312,9 +37309,12 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B7556074-C591-45E1-B532-8E33AF3A1CB7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{447EAC8B-E01C-4BBA-8F26-CA458DD9CFEC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="56e6d1e7-6899-430c-9877-67183cfe1730"/>
+    <ds:schemaRef ds:uri="12ae8c1a-628e-4358-b6c7-76504a3ed5f5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>